--- a/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,29</t>
+          <t>0,0; 14,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,22</t>
+          <t>0,56; 3,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,39</t>
+          <t>0,37; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,63</t>
+          <t>0,67; 2,52</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,65</t>
+          <t>1,26; 6,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,64</t>
+          <t>1,83; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,55</t>
+          <t>1,89; 5,41</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,0</t>
+          <t>0,75; 6,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 15,35</t>
+          <t>2,31; 15,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 9,2</t>
+          <t>2,39; 9,07</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,36</t>
+          <t>0,82; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,74</t>
+          <t>1,61; 3,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,8</t>
+          <t>1,44; 2,81</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4036</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4694</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4141</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5252</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6726</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 9239</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 10440</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5769</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1197; 7331</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>779; 6970</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2869; 10768</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5767</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1439; 7503</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2864; 10756</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5139; 14670</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4774</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>501; 4546</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1591; 10557</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3232; 12269</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5255; 14763</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11755; 28349</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19874; 38627</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,47</t>
+          <t>0,0; 14,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,42</t>
+          <t>0,61; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,28</t>
+          <t>0,34; 2,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,52</t>
+          <t>0,73; 2,53</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,55</t>
+          <t>1,06; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,86</t>
+          <t>1,74; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,41</t>
+          <t>1,93; 5,64</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,84</t>
+          <t>0,77; 6,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 15,32</t>
+          <t>2,61; 15,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,07</t>
+          <t>2,44; 9,74</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,29</t>
+          <t>0,87; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,87</t>
+          <t>1,51; 3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,81</t>
+          <t>1,43; 2,81</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 4246</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4141</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 4864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6726</t>
+          <t>0; 5618</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 9239</t>
+          <t>0; 9255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 10440</t>
+          <t>0; 10578</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1197; 7331</t>
+          <t>1297; 7439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>779; 6970</t>
+          <t>727; 6162</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2869; 10768</t>
+          <t>3106; 10818</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1439; 7503</t>
+          <t>1211; 7623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2864; 10756</t>
+          <t>2724; 10654</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5139; 14670</t>
+          <t>5240; 15308</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>501; 4546</t>
+          <t>515; 4575</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1591; 10557</t>
+          <t>1799; 10431</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3232; 12269</t>
+          <t>3301; 13175</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5255; 14763</t>
+          <t>5610; 15287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11755; 28349</t>
+          <t>11085; 27810</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19874; 38627</t>
+          <t>19689; 38669</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,48</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,73</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,49</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,47</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,9</t>
+          <t>0,63; 3,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,53</t>
+          <t>0,71; 2,73</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,66</t>
+          <t>1,82; 7,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,79</t>
+          <t>1,05; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,64</t>
+          <t>1,97; 5,87</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,89</t>
+          <t>2,94; 15,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 15,14</t>
+          <t>0,68; 6,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,74</t>
+          <t>2,4; 9,27</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,37</t>
+          <t>1,69; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,8</t>
+          <t>0,85; 2,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,81</t>
+          <t>1,46; 2,83</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1111</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3615</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4661</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4246</t>
+          <t>0; 3970</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>824</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1873</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4157</t>
+          <t>0; 5489</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4864</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5618</t>
+          <t>0; 6661</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2288</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 7817</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 9255</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 10578</t>
+          <t>0; 8822</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5313</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1297; 7439</t>
+          <t>665; 6900</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>727; 6162</t>
+          <t>1114; 6183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3106; 10818</t>
+          <t>2649; 10156</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9093</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1211; 7623</t>
+          <t>2584; 10276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2724; 10654</t>
+          <t>1202; 7820</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5240; 15308</t>
+          <t>5043; 15025</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6684</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>515; 4575</t>
+          <t>1923; 10424</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1799; 10431</t>
+          <t>465; 4312</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3301; 13175</t>
+          <t>3209; 12374</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26361</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5610; 15287</t>
+          <t>11350; 25877</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11085; 27810</t>
+          <t>5158; 14923</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19689; 38669</t>
+          <t>18648; 36274</t>
         </is>
       </c>
     </row>
